--- a/data/client-intake/client-intake-checklist.xlsx
+++ b/data/client-intake/client-intake-checklist.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3632,7 +3632,7 @@
       <c r="D82" s="4" t="inlineStr"/>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>vtcr_key looked up in the REQ 52 table, the retain/invest split on a Reward pattern, then the REQ 51 guards and the REQ 25 override</t>
+          <t>vtcr_key looked up in the REQ 52 table, the retain/invest split on an all-pass key, then the REQ 51 guards and the REQ 25 override</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -3815,31 +3815,27 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>infotech_template_disposition</t>
+          <t>is_ai_tool</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>What the licensed reference table returns</t>
+          <t>Is this an AI tool or agent</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr"/>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>vtcr_key looked up in the reference 16-row table</t>
+          <t>REQ 11 classifier over name, vendor and description</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>TRUE | FALSE</t>
         </is>
       </c>
       <c r="G88" s="13" t="inlineStr"/>
-      <c r="H88" s="15" t="inlineStr">
-        <is>
-          <t>Internal only.</t>
-        </is>
-      </c>
+      <c r="H88" s="15" t="inlineStr"/>
       <c r="I88" s="16" t="inlineStr"/>
     </row>
     <row r="89">
@@ -3850,18 +3846,18 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>is_ai_tool</t>
+          <t>is_orphaned</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Is this an AI tool or agent</t>
+          <t>No accountable owner could be established</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr"/>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>REQ 11 classifier over name, vendor and description</t>
+          <t>REQ 18: business_owner and technical_owner both unresolvable after triangulating CMDB, cost centre and SSO</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
@@ -3870,7 +3866,11 @@
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr"/>
-      <c r="H89" s="15" t="inlineStr"/>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>Orphaned plus low usage is the highest-yield, easiest-to-defend elimination candidate.</t>
+        </is>
+      </c>
       <c r="I89" s="16" t="inlineStr"/>
     </row>
     <row r="90">
@@ -3881,18 +3881,18 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>is_orphaned</t>
+          <t>is_shadow_it</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>No accountable owner could be established</t>
+          <t>Paid for or in use but not governed</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr"/>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>REQ 18: business_owner and technical_owner both unresolvable after triangulating CMDB, cost centre and SSO</t>
+          <t>REQ 8: AP spend or SSO activity with no CMDB record</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -3901,11 +3901,7 @@
         </is>
       </c>
       <c r="G90" s="13" t="inlineStr"/>
-      <c r="H90" s="15" t="inlineStr">
-        <is>
-          <t>Orphaned plus low usage is the highest-yield, easiest-to-defend elimination candidate.</t>
-        </is>
-      </c>
+      <c r="H90" s="15" t="inlineStr"/>
       <c r="I90" s="16" t="inlineStr"/>
     </row>
     <row r="91">
@@ -3916,23 +3912,23 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>is_shadow_it</t>
+          <t>licence_utilisation_rate</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Paid for or in use but not governed</t>
+          <t>Share of bought seats actually used</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>REQ 8: AP spend or SSO activity with no CMDB record</t>
+          <t>active_users / licences_purchased</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>TRUE | FALSE</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr"/>
@@ -3947,23 +3943,23 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>licence_utilisation_rate</t>
+          <t>lifecycle_exclusion_applied</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Share of bought seats actually used</t>
+          <t>Birth/Growth guard is armed</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr"/>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>active_users / licences_purchased</t>
+          <t>lifecycle_stage in Birth or Growth (REQ 51)</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>TRUE | FALSE</t>
         </is>
       </c>
       <c r="G92" s="13" t="inlineStr"/>
@@ -3978,23 +3974,23 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>lifecycle_exclusion_applied</t>
+          <t>missing_fields</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Birth/Growth guard is armed</t>
+          <t>Which model-consumed fields are empty</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>lifecycle_stage in Birth or Growth (REQ 51)</t>
+          <t>The empty subset of those 44 fields; 'unknown' counts as empty</t>
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>TRUE | FALSE</t>
+          <t>semicolon-separated list</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr"/>
@@ -4009,23 +4005,23 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>missing_fields</t>
+          <t>net_saving_annual</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Which model-consumed fields are empty</t>
+          <t>Saving after netting</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>The empty subset of those 44 fields; 'unknown' counts as empty</t>
+          <t>gross - successor run cost - amortised one-time - residual archival (REQ 32/54)</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>semicolon-separated list</t>
+          <t>USD per year</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr"/>
@@ -4040,23 +4036,23 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>net_saving_annual</t>
+          <t>net_saving_five_year</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Saving after netting</t>
+          <t>Five-year net saving</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>gross - successor run cost - amortised one-time - residual archival (REQ 32/54)</t>
+          <t>net_saving_annual x 5, undiscounted</t>
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>USD per year</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr"/>
@@ -4071,23 +4067,23 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>net_saving_five_year</t>
+          <t>notice_deadline_date</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Five-year net saving</t>
+          <t>The real deadline to serve notice</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>net_saving_annual x 5, undiscounted</t>
+          <t>term_end - renewal_notice_days</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ISO date</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr"/>
@@ -4102,23 +4098,23 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>notice_deadline_date</t>
+          <t>ov_reach_consumers</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>The real deadline to serve notice</t>
+          <t>V2 - breadth of use</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
       <c r="E97" s="15" t="inlineStr">
         <is>
-          <t>term_end - renewal_notice_days</t>
+          <t>Rubric band over active_users vs licences_purchased (REQ 21)</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>ISO date</t>
+          <t>1-5 in 0.5 steps</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr"/>
@@ -4133,18 +4129,18 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>ov_reach_consumers</t>
+          <t>ov_reduce_costs_efficiency</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>V2 - breadth of use</t>
+          <t>V3 - process centrality</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Rubric band over active_users vs licences_purchased (REQ 21)</t>
+          <t>Rubric band over the process_centrality answer (REQ 21)</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -4153,7 +4149,11 @@
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr"/>
-      <c r="H98" s="15" t="inlineStr"/>
+      <c r="H98" s="15" t="inlineStr">
+        <is>
+          <t>Derived from a tier-4 answer rather than from a system, but still not a field a client fills in twice.</t>
+        </is>
+      </c>
       <c r="I98" s="16" t="inlineStr"/>
     </row>
     <row r="99">
@@ -4164,31 +4164,27 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>ov_reduce_costs_efficiency</t>
+          <t>overlap_cluster_id</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>V3 - process centrality</t>
+          <t>Overlap cluster it belongs to</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
       <c r="E99" s="15" t="inlineStr">
         <is>
-          <t>Rubric band over the process_centrality answer (REQ 21)</t>
+          <t>REQ 25 clustering on capability, feature coverage, user overlap and cost</t>
         </is>
       </c>
       <c r="F99" s="15" t="inlineStr">
         <is>
-          <t>1-5 in 0.5 steps</t>
+          <t>cluster id</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr"/>
-      <c r="H99" s="15" t="inlineStr">
-        <is>
-          <t>Derived from a tier-4 answer rather than from a system, but still not a field a client fills in twice.</t>
-        </is>
-      </c>
+      <c r="H99" s="15" t="inlineStr"/>
       <c r="I99" s="16" t="inlineStr"/>
     </row>
     <row r="100">
@@ -4199,23 +4195,23 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>overlap_cluster_id</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Overlap cluster it belongs to</t>
+          <t>How urgent</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr"/>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>REQ 25 clustering on capability, feature coverage, user overlap and cost</t>
+          <t>The table's priority, stepped by the retention constraint, the successor bump and the override rule</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
-          <t>cluster id</t>
+          <t>Very High to Very Low</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr"/>
@@ -4230,23 +4226,23 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>r_pass</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>How urgent</t>
+          <t>Risk gate</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
       <c r="E101" s="15" t="inlineStr">
         <is>
-          <t>The table's priority, stepped by the retention constraint, the successor bump and the override rule</t>
+          <t>risk_posture_score &gt;= 3.0</t>
         </is>
       </c>
       <c r="F101" s="15" t="inlineStr">
         <is>
-          <t>Very High to Very Low</t>
+          <t>P | F</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr"/>
@@ -4261,27 +4257,31 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>r_pass</t>
+          <t>rationale</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Risk gate</t>
+          <t>The written reason</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr"/>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>risk_posture_score &gt;= 3.0</t>
+          <t>Composed from the gate key, the scores, the evidence and the saving arithmetic (REQ 27)</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>P | F</t>
+          <t>prose</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr"/>
-      <c r="H102" s="15" t="inlineStr"/>
+      <c r="H102" s="15" t="inlineStr">
+        <is>
+          <t>REQ 27: the rationale, not the category, is the deliverable.</t>
+        </is>
+      </c>
       <c r="I102" s="16" t="inlineStr"/>
     </row>
     <row r="103">
@@ -4292,31 +4292,27 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>rationale</t>
+          <t>redundancy_override_applied</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>The written reason</t>
+          <t>Cluster membership forced consolidate</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr"/>
       <c r="E103" s="15" t="inlineStr">
         <is>
-          <t>Composed from the gate key, the scores, the evidence and the saving arithmetic (REQ 27)</t>
+          <t>cluster_role == absorbed (REQ 25)</t>
         </is>
       </c>
       <c r="F103" s="15" t="inlineStr">
         <is>
-          <t>prose</t>
+          <t>TRUE | FALSE</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr"/>
-      <c r="H103" s="15" t="inlineStr">
-        <is>
-          <t>REQ 27: the rationale, not the category, is the deliverable.</t>
-        </is>
-      </c>
+      <c r="H103" s="15" t="inlineStr"/>
       <c r="I103" s="16" t="inlineStr"/>
     </row>
     <row r="104">
@@ -4327,23 +4323,23 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>redundancy_override_applied</t>
+          <t>replacement_app_id</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Cluster membership forced consolidate</t>
+          <t>The named successor</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr"/>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>cluster_role == absorbed (REQ 25)</t>
+          <t>The cluster survivor, or a human-named target (REQ 58)</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>TRUE | FALSE</t>
+          <t>app_id or external label</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr"/>
@@ -4358,27 +4354,31 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>replacement_app_id</t>
+          <t>replacement_cost_already_in_baseline</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>The named successor</t>
+          <t>Successor is already a paid line here</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr"/>
       <c r="E105" s="15" t="inlineStr">
         <is>
-          <t>The cluster survivor, or a human-named target (REQ 58)</t>
+          <t>True when replacement_app_id resolves to a row already in the portfolio</t>
         </is>
       </c>
       <c r="F105" s="15" t="inlineStr">
         <is>
-          <t>app_id or external label</t>
+          <t>TRUE | FALSE</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr"/>
-      <c r="H105" s="15" t="inlineStr"/>
+      <c r="H105" s="15" t="inlineStr">
+        <is>
+          <t>Stops the successor's cost being subtracted twice.</t>
+        </is>
+      </c>
       <c r="I105" s="16" t="inlineStr"/>
     </row>
     <row r="106">
@@ -4389,31 +4389,27 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>replacement_cost_already_in_baseline</t>
+          <t>replacement_ongoing_tco</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Successor is already a paid line here</t>
+          <t>Successor's cost to carry this workload</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>True when replacement_app_id resolves to a row already in the portfolio</t>
+          <t>Looked up from the successor's own annual_tco_recurring</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>TRUE | FALSE</t>
+          <t>USD per year</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr"/>
-      <c r="H106" s="15" t="inlineStr">
-        <is>
-          <t>Stops the successor's cost being subtracted twice.</t>
-        </is>
-      </c>
+      <c r="H106" s="15" t="inlineStr"/>
       <c r="I106" s="16" t="inlineStr"/>
     </row>
     <row r="107">
@@ -4424,23 +4420,23 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>replacement_ongoing_tco</t>
+          <t>retention_override_applied</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>Successor's cost to carry this workload</t>
+          <t>A live retention obligation constrains retire</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="15" t="inlineStr">
         <is>
-          <t>Looked up from the successor's own annual_tco_recurring</t>
+          <t>retire + retention_obligation_flag + retention_expiry_date in the future (REQ 53)</t>
         </is>
       </c>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>USD per year</t>
+          <t>TRUE | FALSE</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr"/>
@@ -4455,27 +4451,31 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>retention_override_applied</t>
+          <t>retain_or_invest_basis</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>A live retention obligation constrains retire</t>
+          <t>Why a row was called retain rather than invest</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>retire + retention_obligation_flag + retention_expiry_date in the future (REQ 53)</t>
+          <t>retain_or_invest(): which dimension fails the gate and is therefore what the money buys, or that none of the four does. Blank on consolidate, replace and retire</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>TRUE | FALSE</t>
+          <t>prose or blank</t>
         </is>
       </c>
       <c r="G108" s="13" t="inlineStr"/>
-      <c r="H108" s="15" t="inlineStr"/>
+      <c r="H108" s="15" t="inlineStr">
+        <is>
+          <t>The audit trail for the five-term vocabulary. New in v2.</t>
+        </is>
+      </c>
       <c r="I108" s="16" t="inlineStr"/>
     </row>
     <row r="109">
@@ -4486,31 +4486,27 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>reward_split_basis</t>
+          <t>risk_posture_score</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Why a Reward row was called retain or invest</t>
+          <t>Risk posture (R)</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="15" t="inlineStr">
         <is>
-          <t>split_reward(): which test of the retain/invest split fired. Blank on every non-Reward pattern</t>
+          <t>Weighted mean of the R criteria (R4 disabled)</t>
         </is>
       </c>
       <c r="F109" s="15" t="inlineStr">
         <is>
-          <t>prose or blank</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr"/>
-      <c r="H109" s="15" t="inlineStr">
-        <is>
-          <t>The audit trail for the five-term vocabulary. New in v2.</t>
-        </is>
-      </c>
+      <c r="H109" s="15" t="inlineStr"/>
       <c r="I109" s="16" t="inlineStr"/>
     </row>
     <row r="110">
@@ -4521,27 +4517,31 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>risk_posture_score</t>
+          <t>saving_type</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Risk posture (R)</t>
+          <t>Recurring, one-time or none</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr"/>
       <c r="E110" s="15" t="inlineStr">
         <is>
-          <t>Weighted mean of the R criteria (R4 disabled)</t>
+          <t>Seeded by the analyst, then forced to 'none' by the engine wherever gross saving is zero</t>
         </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>recurring | one-time | none</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr"/>
-      <c r="H110" s="15" t="inlineStr"/>
+      <c r="H110" s="15" t="inlineStr">
+        <is>
+          <t>The one genuinely hybrid field: the dictionary marks it input, the engine can overwrite it.</t>
+        </is>
+      </c>
       <c r="I110" s="16" t="inlineStr"/>
     </row>
     <row r="111">
@@ -4552,31 +4552,27 @@
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>saving_type</t>
+          <t>sourcing_exclusion_applied</t>
         </is>
       </c>
       <c r="C111" s="15" t="inlineStr">
         <is>
-          <t>Recurring, one-time or none</t>
+          <t>Sourcing made a disposition illegal</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr"/>
       <c r="E111" s="15" t="inlineStr">
         <is>
-          <t>Seeded by the analyst, then forced to 'none' by the engine wherever gross saving is zero</t>
+          <t>sourcing_type SaaS with a replace disposition (REQ 51)</t>
         </is>
       </c>
       <c r="F111" s="15" t="inlineStr">
         <is>
-          <t>recurring | one-time | none</t>
+          <t>TRUE | FALSE</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr"/>
-      <c r="H111" s="15" t="inlineStr">
-        <is>
-          <t>The one genuinely hybrid field: the dictionary marks it input, the engine can overwrite it.</t>
-        </is>
-      </c>
+      <c r="H111" s="15" t="inlineStr"/>
       <c r="I111" s="16" t="inlineStr"/>
     </row>
     <row r="112">
@@ -4587,27 +4583,31 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>sourcing_exclusion_applied</t>
+          <t>suppressed_recommendation</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Sourcing made a disposition illegal</t>
+          <t>What a guard suppressed</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr"/>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t>sourcing_type SaaS with a replace disposition (REQ 51)</t>
+          <t>Recorded whenever a guard changed or armed against the gate result</t>
         </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>TRUE | FALSE</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr"/>
-      <c r="H112" s="15" t="inlineStr"/>
+      <c r="H112" s="15" t="inlineStr">
+        <is>
+          <t>Never silent (REQ 51).</t>
+        </is>
+      </c>
       <c r="I112" s="16" t="inlineStr"/>
     </row>
     <row r="113">
@@ -4618,31 +4618,27 @@
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>suppressed_recommendation</t>
+          <t>suppression_reason</t>
         </is>
       </c>
       <c r="C113" s="15" t="inlineStr">
         <is>
-          <t>What a guard suppressed</t>
+          <t>Why it was suppressed</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr"/>
       <c r="E113" s="15" t="inlineStr">
         <is>
-          <t>Recorded whenever a guard changed or armed against the gate result</t>
+          <t>Accumulated guard reasons</t>
         </is>
       </c>
       <c r="F113" s="15" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>prose</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr"/>
-      <c r="H113" s="15" t="inlineStr">
-        <is>
-          <t>Never silent (REQ 51).</t>
-        </is>
-      </c>
+      <c r="H113" s="15" t="inlineStr"/>
       <c r="I113" s="16" t="inlineStr"/>
     </row>
     <row r="114">
@@ -4653,23 +4649,23 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>suppression_reason</t>
+          <t>t_pass</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Why it was suppressed</t>
+          <t>Technical gate</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr"/>
       <c r="E114" s="15" t="inlineStr">
         <is>
-          <t>Accumulated guard reasons</t>
+          <t>technical_health_score &gt;= 3.0</t>
         </is>
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>prose</t>
+          <t>P | F</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr"/>
@@ -4684,23 +4680,23 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>t_pass</t>
+          <t>tco_five_category_subtotal</t>
         </is>
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>Technical gate</t>
+          <t>The five reference cost categories</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="15" t="inlineStr">
         <is>
-          <t>technical_health_score &gt;= 3.0</t>
+          <t>Sum of the five cost_* components</t>
         </is>
       </c>
       <c r="F115" s="15" t="inlineStr">
         <is>
-          <t>P | F</t>
+          <t>USD per year</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr"/>
@@ -4715,23 +4711,23 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>tco_five_category_subtotal</t>
+          <t>technical_health_score</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>The five reference cost categories</t>
+          <t>Technical health (T)</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr"/>
       <c r="E116" s="15" t="inlineStr">
         <is>
-          <t>Sum of the five cost_* components</t>
+          <t>Weighted mean of the five T criteria</t>
         </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>USD per year</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="G116" s="13" t="inlineStr"/>
@@ -4746,23 +4742,23 @@
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>technical_health_score</t>
+          <t>technical_obsolescence_flag</t>
         </is>
       </c>
       <c r="C117" s="15" t="inlineStr">
         <is>
-          <t>Technical health (T)</t>
+          <t>Obsolescence is material, not notional</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr"/>
       <c r="E117" s="15" t="inlineStr">
         <is>
-          <t>Weighted mean of the five T criteria</t>
+          <t>REQ 17: version_installed vs version_vendor_supported, and vendor_eos_date against the analysis date</t>
         </is>
       </c>
       <c r="F117" s="15" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>TRUE | FALSE</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr"/>
@@ -4777,27 +4773,31 @@
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>technical_obsolescence_flag</t>
+          <t>th_supportability</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Obsolescence is material, not notional</t>
+          <t>T1 - version currency and end-of-support proximity</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr"/>
       <c r="E118" s="15" t="inlineStr">
         <is>
-          <t>REQ 17: version_installed vs version_vendor_supported, and vendor_eos_date against the analysis date</t>
+          <t>Rubric band over version_installed vs version_vendor_supported and vendor_eos_date (REQ 22)</t>
         </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>TRUE | FALSE</t>
+          <t>1-5 in 0.5 steps</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr"/>
-      <c r="H118" s="15" t="inlineStr"/>
+      <c r="H118" s="15" t="inlineStr">
+        <is>
+          <t>WEIGHT 2. Scored here and nowhere else - risk must not re-consume it.</t>
+        </is>
+      </c>
       <c r="I118" s="16" t="inlineStr"/>
     </row>
     <row r="119">
@@ -4808,31 +4808,27 @@
       </c>
       <c r="B119" s="14" t="inlineStr">
         <is>
-          <t>th_supportability</t>
+          <t>unused_licence_count</t>
         </is>
       </c>
       <c r="C119" s="15" t="inlineStr">
         <is>
-          <t>T1 - version currency and end-of-support proximity</t>
+          <t>Licensed but inactive seats</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="15" t="inlineStr">
         <is>
-          <t>Rubric band over version_installed vs version_vendor_supported and vendor_eos_date (REQ 22)</t>
+          <t>licences_purchased - active_users</t>
         </is>
       </c>
       <c r="F119" s="15" t="inlineStr">
         <is>
-          <t>1-5 in 0.5 steps</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr"/>
-      <c r="H119" s="15" t="inlineStr">
-        <is>
-          <t>WEIGHT 2. Scored here and nowhere else - risk must not re-consume it.</t>
-        </is>
-      </c>
+      <c r="H119" s="15" t="inlineStr"/>
       <c r="I119" s="16" t="inlineStr"/>
     </row>
     <row r="120">
@@ -4843,23 +4839,23 @@
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>unused_licence_count</t>
+          <t>unused_licence_spend</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Licensed but inactive seats</t>
+          <t>Licence spend on inactive seats</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr"/>
       <c r="E120" s="15" t="inlineStr">
         <is>
-          <t>licences_purchased - active_users</t>
+          <t>cost_licence_subscription x (1 - licence_utilisation_rate)</t>
         </is>
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>USD per year</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr"/>
@@ -4874,23 +4870,23 @@
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>unused_licence_spend</t>
+          <t>urg_timeline_sensitivity</t>
         </is>
       </c>
       <c r="C121" s="15" t="inlineStr">
         <is>
-          <t>Licence spend on inactive seats</t>
+          <t>How time-bound the decision is</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="15" t="inlineStr">
         <is>
-          <t>cost_licence_subscription x (1 - licence_utilisation_rate)</t>
+          <t>Bands over term_end, notice_deadline_date and vendor_eos_date (REQ 56)</t>
         </is>
       </c>
       <c r="F121" s="15" t="inlineStr">
         <is>
-          <t>USD per year</t>
+          <t>High | Medium | Low | None</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr"/>
@@ -4905,23 +4901,23 @@
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>urg_timeline_sensitivity</t>
+          <t>urgency_score</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>How time-bound the decision is</t>
+          <t>Urgency, 0-1</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr"/>
       <c r="E122" s="15" t="inlineStr">
         <is>
-          <t>Bands over term_end, notice_deadline_date and vendor_eos_date (REQ 56)</t>
+          <t>Mean of the two urgency bands</t>
         </is>
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
-          <t>High | Medium | Low | None</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr"/>
@@ -4936,23 +4932,23 @@
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
-          <t>urgency_score</t>
+          <t>v_pass</t>
         </is>
       </c>
       <c r="C123" s="15" t="inlineStr">
         <is>
-          <t>Urgency, 0-1</t>
+          <t>Value gate</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr"/>
       <c r="E123" s="15" t="inlineStr">
         <is>
-          <t>Mean of the two urgency bands</t>
+          <t>business_value_score &gt;= 3.0</t>
         </is>
       </c>
       <c r="F123" s="15" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>P | F</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr"/>
@@ -4967,27 +4963,31 @@
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>v_pass</t>
+          <t>vendor_eos_date</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Value gate</t>
+          <t>Vendor end-of-support date</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr"/>
       <c r="E124" s="15" t="inlineStr">
         <is>
-          <t>business_value_score &gt;= 3.0</t>
+          <t>Vendor lifecycle lookup by the tool</t>
         </is>
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
-          <t>P | F</t>
+          <t>ISO date</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr"/>
-      <c r="H124" s="15" t="inlineStr"/>
+      <c r="H124" s="15" t="inlineStr">
+        <is>
+          <t>Deliberately excluded from the completeness denominator: a SaaS product legitimately has none.</t>
+        </is>
+      </c>
       <c r="I124" s="16" t="inlineStr"/>
     </row>
     <row r="125">
@@ -4998,31 +4998,27 @@
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>vendor_eos_date</t>
+          <t>version_vendor_supported</t>
         </is>
       </c>
       <c r="C125" s="15" t="inlineStr">
         <is>
-          <t>Vendor end-of-support date</t>
+          <t>Version the vendor currently supports</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr"/>
       <c r="E125" s="15" t="inlineStr">
         <is>
-          <t>Vendor lifecycle lookup by the tool</t>
+          <t>Vendor lifecycle lookup by the tool, not a client field</t>
         </is>
       </c>
       <c r="F125" s="15" t="inlineStr">
         <is>
-          <t>ISO date</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr"/>
-      <c r="H125" s="15" t="inlineStr">
-        <is>
-          <t>Deliberately excluded from the completeness denominator: a SaaS product legitimately has none.</t>
-        </is>
-      </c>
+      <c r="H125" s="15" t="inlineStr"/>
       <c r="I125" s="16" t="inlineStr"/>
     </row>
     <row r="126">
@@ -5033,59 +5029,28 @@
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>version_vendor_supported</t>
+          <t>vtcr_key</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Version the vendor currently supports</t>
+          <t>The four gates concatenated</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr"/>
       <c r="E126" s="15" t="inlineStr">
         <is>
-          <t>Vendor lifecycle lookup by the tool, not a client field</t>
+          <t>v_pass + t_pass + c_pass + r_pass</t>
         </is>
       </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>e.g. PPFP</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr"/>
       <c r="H126" s="15" t="inlineStr"/>
       <c r="I126" s="16" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="13" t="inlineStr">
-        <is>
-          <t>5 - Tool derives (nothing to send)</t>
-        </is>
-      </c>
-      <c r="B127" s="14" t="inlineStr">
-        <is>
-          <t>vtcr_key</t>
-        </is>
-      </c>
-      <c r="C127" s="15" t="inlineStr">
-        <is>
-          <t>The four gates concatenated</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr"/>
-      <c r="E127" s="15" t="inlineStr">
-        <is>
-          <t>v_pass + t_pass + c_pass + r_pass</t>
-        </is>
-      </c>
-      <c r="F127" s="15" t="inlineStr">
-        <is>
-          <t>e.g. PPFP</t>
-        </is>
-      </c>
-      <c r="G127" s="13" t="inlineStr"/>
-      <c r="H127" s="15" t="inlineStr"/>
-      <c r="I127" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I127"/>
